--- a/base_consolidada_copel.xlsx
+++ b/base_consolidada_copel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2C65EA33E46BBC01/Documentos/GitHub/Copel/BI-Cadastro/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="202" documentId="8_{3B56D86A-9EAD-4F2D-9E3E-22B01AFB0494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E27B955F-1001-471E-ABA4-58D793097AA0}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="8_{3B56D86A-9EAD-4F2D-9E3E-22B01AFB0494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D403833-EC48-4863-9F72-46ED57FE39FB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8AB9A13F-44E0-4B3C-96AE-DCD14FFC03F2}"/>
   </bookViews>
@@ -3592,6 +3592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D65FC96-6C7E-46D3-91CD-DD3773AB5849}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AL239"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3749,7 +3750,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>4161165</v>
       </c>
@@ -3847,7 +3848,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>7003455</v>
       </c>
@@ -3945,7 +3946,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>10418148</v>
       </c>
@@ -4040,7 +4041,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>18576230</v>
       </c>
@@ -4135,7 +4136,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>18849512</v>
       </c>
@@ -4233,7 +4234,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>24017833</v>
       </c>
@@ -4331,7 +4332,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26353261</v>
       </c>
@@ -4426,7 +4427,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>37542001</v>
       </c>
@@ -4521,7 +4522,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>53832540</v>
       </c>
@@ -4619,7 +4620,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>54782406</v>
       </c>
@@ -4714,7 +4715,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>67575153</v>
       </c>
@@ -4812,7 +4813,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>68449933</v>
       </c>
@@ -4907,7 +4908,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>71460969</v>
       </c>
@@ -5005,7 +5006,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>73661783</v>
       </c>
@@ -5100,7 +5101,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>78620929</v>
       </c>
@@ -5198,7 +5199,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>84569093</v>
       </c>
@@ -5296,7 +5297,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>87093561</v>
       </c>
@@ -5394,7 +5395,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>88396371</v>
       </c>
@@ -5492,7 +5493,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>91526370</v>
       </c>
@@ -5590,7 +5591,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>92124240</v>
       </c>
@@ -5688,7 +5689,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>92187595</v>
       </c>
@@ -5783,7 +5784,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>94617546</v>
       </c>
@@ -5881,7 +5882,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>96579137</v>
       </c>
@@ -5979,7 +5980,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>98555413</v>
       </c>
@@ -6077,7 +6078,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>99213451</v>
       </c>
@@ -6175,7 +6176,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>99506890</v>
       </c>
@@ -6273,7 +6274,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>99509725</v>
       </c>
@@ -6371,7 +6372,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>100124992</v>
       </c>
@@ -6466,7 +6467,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>101341792</v>
       </c>
@@ -6564,7 +6565,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>101474237</v>
       </c>
@@ -6662,7 +6663,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>102006288</v>
       </c>
@@ -6760,7 +6761,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>102197784</v>
       </c>
@@ -6855,7 +6856,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>102270180</v>
       </c>
@@ -6953,7 +6954,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>103764941</v>
       </c>
@@ -7051,7 +7052,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>105667226</v>
       </c>
@@ -7131,7 +7132,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>107056143</v>
       </c>
@@ -7229,7 +7230,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>107778963</v>
       </c>
@@ -7327,7 +7328,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>108488675</v>
       </c>
@@ -7425,7 +7426,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>109529626</v>
       </c>
@@ -7523,7 +7524,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>110240693</v>
       </c>
@@ -7621,7 +7622,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>112138667</v>
       </c>
@@ -7719,7 +7720,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>112309224</v>
       </c>
@@ -7817,7 +7818,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>112868290</v>
       </c>
@@ -7915,7 +7916,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>113440944</v>
       </c>
@@ -8013,7 +8014,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>81764707</v>
       </c>
@@ -8111,7 +8112,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1917455</v>
       </c>
@@ -8206,7 +8207,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>79878830</v>
       </c>
@@ -8301,7 +8302,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>68646844</v>
       </c>
@@ -8402,7 +8403,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>107295245</v>
       </c>
@@ -8509,7 +8510,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>87210240</v>
       </c>
@@ -8613,7 +8614,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>5902126</v>
       </c>
@@ -8717,7 +8718,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>106318284</v>
       </c>
@@ -8818,7 +8819,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>94265127</v>
       </c>
@@ -8922,7 +8923,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>29684030</v>
       </c>
@@ -9029,7 +9030,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>39078655</v>
       </c>
@@ -9136,7 +9137,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>47916303</v>
       </c>
@@ -9240,7 +9241,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>77808541</v>
       </c>
@@ -9347,7 +9348,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>95051147</v>
       </c>
@@ -9454,7 +9455,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>33722420</v>
       </c>
@@ -9561,7 +9562,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>7128118</v>
       </c>
@@ -9665,7 +9666,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>4295439</v>
       </c>
@@ -9769,7 +9770,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>88946185</v>
       </c>
@@ -9876,7 +9877,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>11578912</v>
       </c>
@@ -9983,7 +9984,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="65" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>49970836</v>
       </c>
@@ -10090,7 +10091,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>92989845</v>
       </c>
@@ -10194,7 +10195,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>95108980</v>
       </c>
@@ -10301,7 +10302,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>104071460</v>
       </c>
@@ -10408,7 +10409,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>101202237</v>
       </c>
@@ -10515,7 +10516,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>107523027</v>
       </c>
@@ -10622,7 +10623,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>98367234</v>
       </c>
@@ -10726,7 +10727,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="72" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>66041813</v>
       </c>
@@ -10830,7 +10831,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>103445781</v>
       </c>
@@ -10937,7 +10938,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>111474060</v>
       </c>
@@ -11044,7 +11045,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>63985098</v>
       </c>
@@ -11151,7 +11152,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>89911369</v>
       </c>
@@ -11258,7 +11259,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>90366565</v>
       </c>
@@ -11362,7 +11363,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>86085697</v>
       </c>
@@ -11466,7 +11467,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="79" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>81750161</v>
       </c>
@@ -11573,7 +11574,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>103085459</v>
       </c>
@@ -11787,7 +11788,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>70099898</v>
       </c>
@@ -11891,7 +11892,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>41200144</v>
       </c>
@@ -11995,7 +11996,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>7111665</v>
       </c>
@@ -12102,7 +12103,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>92963633</v>
       </c>
@@ -12206,7 +12207,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85700070</v>
       </c>
@@ -12313,7 +12314,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>83255818</v>
       </c>
@@ -12420,7 +12421,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>106306766</v>
       </c>
@@ -12527,7 +12528,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>96232790</v>
       </c>
@@ -12634,7 +12635,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>104242701</v>
       </c>
@@ -12741,7 +12742,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>48061980</v>
       </c>
@@ -12848,7 +12849,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>72311673</v>
       </c>
@@ -12955,7 +12956,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>88170306</v>
       </c>
@@ -13062,7 +13063,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93911335</v>
       </c>
@@ -13169,7 +13170,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>81364318</v>
       </c>
@@ -13276,7 +13277,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>103429573</v>
       </c>
@@ -13383,7 +13384,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>69672911</v>
       </c>
@@ -13490,7 +13491,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>107896214</v>
       </c>
@@ -13597,7 +13598,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>76908623</v>
       </c>
@@ -13704,7 +13705,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>74629565</v>
       </c>
@@ -13811,7 +13812,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>89305566</v>
       </c>
@@ -13918,7 +13919,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>73130141</v>
       </c>
@@ -14022,7 +14023,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>92657524</v>
       </c>
@@ -14129,7 +14130,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>92480950</v>
       </c>
@@ -14233,7 +14234,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>92156053</v>
       </c>
@@ -14340,7 +14341,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>112310338</v>
       </c>
@@ -14447,7 +14448,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106186256</v>
       </c>
@@ -14554,7 +14555,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>111149053</v>
       </c>
@@ -14661,7 +14662,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>73741736</v>
       </c>
@@ -14765,7 +14766,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>84414278</v>
       </c>
@@ -14872,7 +14873,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110338901</v>
       </c>
@@ -14979,7 +14980,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>97748633</v>
       </c>
@@ -15086,7 +15087,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="113" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>93791992</v>
       </c>
@@ -15190,7 +15191,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="114" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>49814141</v>
       </c>
@@ -15294,7 +15295,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="115" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>4050096</v>
       </c>
@@ -15401,7 +15402,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="116" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>79387730</v>
       </c>
@@ -15508,7 +15509,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="117" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>84197773</v>
       </c>
@@ -15612,7 +15613,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="118" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>13898132</v>
       </c>
@@ -15716,7 +15717,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="119" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>28281209</v>
       </c>
@@ -15823,7 +15824,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="120" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>97430617</v>
       </c>
@@ -15927,7 +15928,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="121" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>9359117</v>
       </c>
@@ -16037,7 +16038,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>11560517</v>
       </c>
@@ -16144,7 +16145,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>82739641</v>
       </c>
@@ -16251,7 +16252,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>112895166</v>
       </c>
@@ -16358,7 +16359,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="125" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>110832639</v>
       </c>
@@ -16465,7 +16466,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="126" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>89671660</v>
       </c>
@@ -16572,7 +16573,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="127" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>104550996</v>
       </c>
@@ -16676,7 +16677,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="128" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>90530055</v>
       </c>
@@ -16783,7 +16784,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="129" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>58978585</v>
       </c>
@@ -16890,7 +16891,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="130" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>108430766</v>
       </c>
@@ -16997,7 +16998,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="131" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>110719255</v>
       </c>
@@ -17101,7 +17102,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="132" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>93121954</v>
       </c>
@@ -17208,7 +17209,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="133" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>98594931</v>
       </c>
@@ -17312,7 +17313,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="134" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>103143009</v>
       </c>
@@ -17419,7 +17420,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="135" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>105493228</v>
       </c>
@@ -17523,7 +17524,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="136" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>99551276</v>
       </c>
@@ -17630,7 +17631,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="137" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>94000948</v>
       </c>
@@ -17737,7 +17738,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="138" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>10229426</v>
       </c>
@@ -17844,7 +17845,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="139" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>88785122</v>
       </c>
@@ -17951,7 +17952,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="140" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>80609031</v>
       </c>
@@ -18055,7 +18056,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="141" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>40501523</v>
       </c>
@@ -18159,7 +18160,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="142" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>79328628</v>
       </c>
@@ -18266,7 +18267,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="143" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>103218068</v>
       </c>
@@ -18370,7 +18371,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="144" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>88120317</v>
       </c>
@@ -18474,7 +18475,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="145" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>67208355</v>
       </c>
@@ -18581,7 +18582,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="146" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>93559232</v>
       </c>
@@ -18685,7 +18686,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="147" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>72913746</v>
       </c>
@@ -18789,7 +18790,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="148" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>98349171</v>
       </c>
@@ -18893,7 +18894,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="149" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>78163650</v>
       </c>
@@ -18997,7 +18998,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="150" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>74211200</v>
       </c>
@@ -19101,7 +19102,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="151" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>93877226</v>
       </c>
@@ -19205,7 +19206,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="152" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>95723340</v>
       </c>
@@ -19309,7 +19310,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="153" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>97944858</v>
       </c>
@@ -19416,7 +19417,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="154" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>110995996</v>
       </c>
@@ -19520,7 +19521,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="155" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>94648794</v>
       </c>
@@ -19624,7 +19625,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="156" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>21372039</v>
       </c>
@@ -19731,7 +19732,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="157" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>43879870</v>
       </c>
@@ -19838,7 +19839,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="158" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>91737222</v>
       </c>
@@ -19945,7 +19946,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="159" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>91337860</v>
       </c>
@@ -20052,7 +20053,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="160" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>44649444</v>
       </c>
@@ -20159,7 +20160,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="161" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>88673987</v>
       </c>
@@ -20263,7 +20264,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="162" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>74496751</v>
       </c>
@@ -20370,7 +20371,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="163" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>105654078</v>
       </c>
@@ -20474,7 +20475,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="164" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>92035434</v>
       </c>
@@ -20581,7 +20582,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="165" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>110701682</v>
       </c>
@@ -20688,7 +20689,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="166" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>18084770</v>
       </c>
@@ -20795,7 +20796,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="167" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>106564064</v>
       </c>
@@ -20902,7 +20903,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="168" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>96636076</v>
       </c>
@@ -21009,7 +21010,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="169" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>36262471</v>
       </c>
@@ -21116,7 +21117,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="170" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>109671198</v>
       </c>
@@ -21223,7 +21224,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="171" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>92410146</v>
       </c>
@@ -21330,7 +21331,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="172" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>86830635</v>
       </c>
@@ -21437,7 +21438,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="173" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>97151050</v>
       </c>
@@ -21541,7 +21542,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="174" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>90860977</v>
       </c>
@@ -21645,7 +21646,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="175" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>90938267</v>
       </c>
@@ -21752,7 +21753,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="176" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>110572408</v>
       </c>
@@ -21856,7 +21857,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="177" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>107977940</v>
       </c>
@@ -21963,7 +21964,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="178" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>90659066</v>
       </c>
@@ -22070,7 +22071,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="179" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>57650144</v>
       </c>
@@ -22177,7 +22178,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="180" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>76842762</v>
       </c>
@@ -22281,7 +22282,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="181" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>98012975</v>
       </c>
@@ -22388,7 +22389,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="182" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>102666148</v>
       </c>
@@ -22495,7 +22496,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="183" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>8477647</v>
       </c>
@@ -22599,7 +22600,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="184" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>82166749</v>
       </c>
@@ -22706,7 +22707,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="185" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>77630769</v>
       </c>
@@ -22810,7 +22811,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="186" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>97400602</v>
       </c>
@@ -22917,7 +22918,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="187" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>79792634</v>
       </c>
@@ -23024,7 +23025,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="188" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>71910719</v>
       </c>
@@ -23131,7 +23132,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="189" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>84955007</v>
       </c>
@@ -23238,7 +23239,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="190" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>94503087</v>
       </c>
@@ -23345,7 +23346,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="191" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>95519190</v>
       </c>
@@ -23449,7 +23450,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="192" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>67788289</v>
       </c>
@@ -23556,7 +23557,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="193" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>93126786</v>
       </c>
@@ -23660,7 +23661,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="194" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>10688595</v>
       </c>
@@ -23767,7 +23768,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="195" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>86535064</v>
       </c>
@@ -23871,7 +23872,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="196" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>91375444</v>
       </c>
@@ -23978,7 +23979,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="197" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>107189828</v>
       </c>
@@ -24085,7 +24086,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="198" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>88686043</v>
       </c>
@@ -24192,7 +24193,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="199" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>109846869</v>
       </c>
@@ -24299,7 +24300,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="200" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>105666653</v>
       </c>
@@ -24403,7 +24404,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="201" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>104582030</v>
       </c>
@@ -24510,7 +24511,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="202" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>19885679</v>
       </c>
@@ -24614,7 +24615,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="203" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>3942430</v>
       </c>
@@ -24721,7 +24722,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="204" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>88811220</v>
       </c>
@@ -24831,7 +24832,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="205" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>84131144</v>
       </c>
@@ -24935,7 +24936,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="206" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>98451766</v>
       </c>
@@ -25039,7 +25040,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="207" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>106135546</v>
       </c>
@@ -25146,7 +25147,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="208" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>75148536</v>
       </c>
@@ -25253,7 +25254,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="209" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>109723260</v>
       </c>
@@ -25357,7 +25358,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="210" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>10551182</v>
       </c>
@@ -25461,7 +25462,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="211" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>6612725</v>
       </c>
@@ -25565,7 +25566,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="212" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>112453570</v>
       </c>
@@ -25672,7 +25673,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="213" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>90216806</v>
       </c>
@@ -25776,7 +25777,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="214" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>102446121</v>
       </c>
@@ -25880,7 +25881,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="215" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>101675062</v>
       </c>
@@ -25984,7 +25985,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="216" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>23678593</v>
       </c>
@@ -26091,7 +26092,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="217" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>92941192</v>
       </c>
@@ -26195,7 +26196,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="218" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>98830376</v>
       </c>
@@ -26302,7 +26303,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="219" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>95786406</v>
       </c>
@@ -26406,7 +26407,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="220" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>96263881</v>
       </c>
@@ -26510,7 +26511,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="221" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>63759578</v>
       </c>
@@ -26617,7 +26618,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="222" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>93164742</v>
       </c>
@@ -26724,7 +26725,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="223" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>19556870</v>
       </c>
@@ -26828,7 +26829,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="224" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>107233975</v>
       </c>
@@ -26935,7 +26936,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="225" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>108939154</v>
       </c>
@@ -27036,7 +27037,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="226" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>91887801</v>
       </c>
@@ -27143,7 +27144,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="227" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>80232795</v>
       </c>
@@ -27250,7 +27251,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="228" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>96507284</v>
       </c>
@@ -27357,7 +27358,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="229" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>105145530</v>
       </c>
@@ -27464,7 +27465,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="230" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>108042499</v>
       </c>
@@ -27568,7 +27569,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="231" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>92680356</v>
       </c>
@@ -27672,7 +27673,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="232" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>103443452</v>
       </c>
@@ -27779,7 +27780,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="233" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>95962468</v>
       </c>
@@ -27883,7 +27884,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="234" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>105639087</v>
       </c>
@@ -27990,7 +27991,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="235" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>98761196</v>
       </c>
@@ -28094,7 +28095,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="236" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>114919151</v>
       </c>
@@ -28198,7 +28199,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="237" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>10039589</v>
       </c>
@@ -28305,7 +28306,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="238" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>103518517</v>
       </c>
@@ -28412,7 +28413,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="239" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:38" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>81649282</v>
       </c>
@@ -28518,6 +28519,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL239" xr:uid="{2D65FC96-6C7E-46D3-91CD-DD3773AB5849}">
+    <filterColumn colId="13">
+      <filters>
+        <filter val="MR"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AL239">
       <sortCondition ref="V1:V239"/>
     </sortState>
